--- a/Team-Data/2008-09/3-21-2008-09.xlsx
+++ b/Team-Data/2008-09/3-21-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E2" t="n">
         <v>41</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>0.586</v>
+        <v>0.594</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J2" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>0.46</v>
@@ -691,10 +758,10 @@
         <v>20</v>
       </c>
       <c r="N2" t="n">
-        <v>0.364</v>
+        <v>0.363</v>
       </c>
       <c r="O2" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P2" t="n">
         <v>25.3</v>
@@ -724,28 +791,28 @@
         <v>4.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA2" t="n">
         <v>20.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -754,13 +821,13 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ2" t="n">
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
@@ -769,10 +836,10 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
         <v>12</v>
@@ -781,7 +848,7 @@
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
         <v>19</v>
@@ -799,7 +866,7 @@
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>8</v>
@@ -808,13 +875,13 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -858,43 +925,43 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
         <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
         <v>42.5</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.7</v>
@@ -909,19 +976,19 @@
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.3</v>
+        <v>101.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -957,16 +1024,16 @@
         <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -978,22 +1045,22 @@
         <v>27</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA3" t="n">
         <v>5</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4" t="n">
         <v>31</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>0.443</v>
+        <v>0.449</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1046,37 +1113,37 @@
         <v>76.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M4" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O4" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P4" t="n">
         <v>23.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.744</v>
+        <v>0.748</v>
       </c>
       <c r="R4" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S4" t="n">
         <v>28.8</v>
       </c>
       <c r="T4" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="U4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V4" t="n">
         <v>15.5</v>
@@ -1088,25 +1155,25 @@
         <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA4" t="n">
         <v>20.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.5</v>
+        <v>93.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
@@ -1115,7 +1182,7 @@
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1133,37 +1200,37 @@
         <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP4" t="n">
         <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
         <v>27</v>
       </c>
       <c r="AU4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1172,13 +1239,13 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -1210,22 +1277,22 @@
         <v>69</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.449</v>
+        <v>0.464</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0.452</v>
@@ -1240,31 +1307,31 @@
         <v>0.381</v>
       </c>
       <c r="O5" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="R5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S5" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
         <v>42.6</v>
       </c>
       <c r="U5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V5" t="n">
         <v>15</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X5" t="n">
         <v>5.5</v>
@@ -1273,19 +1340,19 @@
         <v>5.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
         <v>101.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1315,10 +1382,10 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1327,19 +1394,19 @@
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
         <v>10</v>
@@ -1354,10 +1421,10 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
         <v>19</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -1392,25 +1459,25 @@
         <v>68</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.824</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L6" t="n">
         <v>8</v>
@@ -1419,16 +1486,16 @@
         <v>20.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.389</v>
+        <v>0.386</v>
       </c>
       <c r="O6" t="n">
         <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R6" t="n">
         <v>10.8</v>
@@ -1437,13 +1504,13 @@
         <v>30.9</v>
       </c>
       <c r="T6" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
@@ -1452,22 +1519,22 @@
         <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
         <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.5</v>
+        <v>100.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1491,16 +1558,16 @@
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
         <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1512,19 +1579,19 @@
         <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
         <v>6</v>
@@ -1536,7 +1603,7 @@
         <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1670,10 +1737,10 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM7" t="n">
         <v>9</v>
@@ -1691,10 +1758,10 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>5</v>
@@ -1703,7 +1770,7 @@
         <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>17</v>
@@ -1721,7 +1788,7 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
@@ -1873,13 +1940,13 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
         <v>13</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU8" t="n">
         <v>5</v>
@@ -1888,7 +1955,7 @@
         <v>26</v>
       </c>
       <c r="AW8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
@@ -2064,7 +2131,7 @@
         <v>17</v>
       </c>
       <c r="AU9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2073,7 +2140,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY9" t="n">
         <v>6</v>
@@ -2082,7 +2149,7 @@
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2246,7 +2313,7 @@
         <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO11" t="n">
         <v>13</v>
@@ -2431,16 +2498,16 @@
         <v>19</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
@@ -2452,7 +2519,7 @@
         <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
         <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>0.408</v>
+        <v>0.4</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,16 +2566,16 @@
         <v>38.7</v>
       </c>
       <c r="J12" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M12" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N12" t="n">
         <v>0.376</v>
@@ -2523,19 +2590,19 @@
         <v>0.805</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S12" t="n">
         <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U12" t="n">
         <v>21.8</v>
       </c>
       <c r="V12" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W12" t="n">
         <v>7</v>
@@ -2553,13 +2620,13 @@
         <v>21.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.9</v>
+        <v>103.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2568,10 +2635,10 @@
         <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
         <v>5</v>
@@ -2592,7 +2659,7 @@
         <v>9</v>
       </c>
       <c r="AO12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP12" t="n">
         <v>24</v>
@@ -2601,7 +2668,7 @@
         <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
@@ -2613,10 +2680,10 @@
         <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2625,7 +2692,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA12" t="n">
         <v>13</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
       </c>
       <c r="AF13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH13" t="n">
         <v>7</v>
@@ -2780,34 +2847,34 @@
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS13" t="n">
         <v>26</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>25</v>
       </c>
       <c r="AT13" t="n">
         <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV13" t="n">
         <v>19</v>
       </c>
       <c r="AW13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -2860,19 +2927,19 @@
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="K14" t="n">
         <v>0.478</v>
       </c>
       <c r="L14" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
         <v>0.366</v>
@@ -2881,49 +2948,49 @@
         <v>19.9</v>
       </c>
       <c r="P14" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.766</v>
+        <v>0.77</v>
       </c>
       <c r="R14" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
-        <v>44.2</v>
+        <v>44.4</v>
       </c>
       <c r="U14" t="n">
         <v>23.5</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.4</v>
+        <v>108.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2947,7 +3014,7 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM14" t="n">
         <v>14</v>
@@ -2959,16 +3026,16 @@
         <v>9</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2980,16 +3047,16 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -3027,52 +3094,52 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>0.246</v>
+        <v>0.25</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="J15" t="n">
-        <v>77.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O15" t="n">
         <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
         <v>0.755</v>
       </c>
       <c r="R15" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S15" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="T15" t="n">
         <v>38.9</v>
@@ -3096,16 +3163,16 @@
         <v>21.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3126,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3147,7 +3214,7 @@
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
         <v>29</v>
@@ -3162,10 +3229,10 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3350,7 +3417,7 @@
         <v>4</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -3406,13 +3473,13 @@
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J17" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L17" t="n">
         <v>6</v>
@@ -3421,10 +3488,10 @@
         <v>16.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P17" t="n">
         <v>25.8</v>
@@ -3436,19 +3503,19 @@
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X17" t="n">
         <v>3.8</v>
@@ -3457,34 +3524,34 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="AA17" t="n">
         <v>22.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="AC17" t="n">
         <v>-0.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH17" t="n">
         <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
@@ -3502,7 +3569,7 @@
         <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP17" t="n">
         <v>9</v>
@@ -3511,7 +3578,7 @@
         <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
         <v>24</v>
@@ -3523,16 +3590,16 @@
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3544,7 +3611,7 @@
         <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,7 +3730,7 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>20</v>
@@ -3857,13 +3924,13 @@
         <v>22</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO19" t="n">
         <v>14</v>
@@ -3881,10 +3948,10 @@
         <v>21</v>
       </c>
       <c r="AT19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU19" t="n">
         <v>25</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>26</v>
       </c>
       <c r="AV19" t="n">
         <v>9</v>
@@ -3905,10 +3972,10 @@
         <v>18</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF20" t="n">
         <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4048,7 +4115,7 @@
         <v>14</v>
       </c>
       <c r="AO20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP20" t="n">
         <v>27</v>
@@ -4063,7 +4130,7 @@
         <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU20" t="n">
         <v>27</v>
@@ -4072,7 +4139,7 @@
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
         <v>24</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" t="n">
         <v>28</v>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4143,73 +4210,73 @@
         <v>0.443</v>
       </c>
       <c r="L21" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="M21" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O21" t="n">
         <v>18.4</v>
       </c>
       <c r="P21" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.788</v>
+        <v>0.789</v>
       </c>
       <c r="R21" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S21" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T21" t="n">
         <v>42.3</v>
       </c>
       <c r="U21" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W21" t="n">
         <v>7.3</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB21" t="n">
         <v>105.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="n">
         <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4239,7 +4306,7 @@
         <v>8</v>
       </c>
       <c r="AR21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
         <v>8</v>
@@ -4248,13 +4315,13 @@
         <v>9</v>
       </c>
       <c r="AU21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV21" t="n">
         <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>24</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4391,7 +4458,7 @@
         <v>26</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>16</v>
@@ -4400,7 +4467,7 @@
         <v>10</v>
       </c>
       <c r="AK22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4424,7 +4491,7 @@
         <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT22" t="n">
         <v>4</v>
@@ -4445,7 +4512,7 @@
         <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
         <v>20</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -4483,22 +4550,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E23" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F23" t="n">
         <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>0.739</v>
+        <v>0.735</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J23" t="n">
         <v>78.2</v>
@@ -4510,7 +4577,7 @@
         <v>10.3</v>
       </c>
       <c r="M23" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="N23" t="n">
         <v>0.387</v>
@@ -4522,19 +4589,19 @@
         <v>27.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="R23" t="n">
         <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="T23" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V23" t="n">
         <v>14.3</v>
@@ -4552,16 +4619,16 @@
         <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.3</v>
+        <v>102.1</v>
       </c>
       <c r="AC23" t="n">
         <v>7.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4618,10 +4685,10 @@
         <v>16</v>
       </c>
       <c r="AW23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY23" t="n">
         <v>2</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4825,7 @@
         <v>27</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -4847,43 +4914,43 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F25" t="n">
         <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.551</v>
+        <v>0.544</v>
       </c>
       <c r="H25" t="n">
         <v>48.1</v>
       </c>
       <c r="I25" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="J25" t="n">
-        <v>80.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.506</v>
+        <v>0.505</v>
       </c>
       <c r="L25" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M25" t="n">
         <v>17.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.385</v>
+        <v>0.382</v>
       </c>
       <c r="O25" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="P25" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q25" t="n">
         <v>0.755</v>
@@ -4892,40 +4959,40 @@
         <v>10.4</v>
       </c>
       <c r="S25" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U25" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V25" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W25" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>108.7</v>
+        <v>108.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4958,7 +5025,7 @@
         <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP25" t="n">
         <v>5</v>
@@ -4970,7 +5037,7 @@
         <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
         <v>16</v>
@@ -4979,7 +5046,7 @@
         <v>3</v>
       </c>
       <c r="AV25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW25" t="n">
         <v>24</v>
@@ -4994,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
         <v>2</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -5032,25 +5099,25 @@
         <v>69</v>
       </c>
       <c r="E26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
-        <v>0.638</v>
+        <v>0.623</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
         <v>79</v>
       </c>
       <c r="K26" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
@@ -5062,25 +5129,25 @@
         <v>0.38</v>
       </c>
       <c r="O26" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.768</v>
+        <v>0.766</v>
       </c>
       <c r="R26" t="n">
         <v>12.8</v>
       </c>
       <c r="S26" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="T26" t="n">
         <v>41.4</v>
       </c>
       <c r="U26" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V26" t="n">
         <v>12.8</v>
@@ -5092,37 +5159,37 @@
         <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA26" t="n">
         <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99</v>
+        <v>98.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="n">
         <v>23</v>
@@ -5140,13 +5207,13 @@
         <v>8</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR26" t="n">
         <v>2</v>
@@ -5158,7 +5225,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5179,10 +5246,10 @@
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5310,7 +5377,7 @@
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
         <v>12</v>
@@ -5319,7 +5386,7 @@
         <v>12</v>
       </c>
       <c r="AN27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5334,7 +5401,7 @@
         <v>27</v>
       </c>
       <c r="AS27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT27" t="n">
         <v>30</v>
@@ -5343,7 +5410,7 @@
         <v>28</v>
       </c>
       <c r="AV27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW27" t="n">
         <v>18</v>
@@ -5355,7 +5422,7 @@
         <v>20</v>
       </c>
       <c r="AZ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
         <v>11</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5546,7 +5613,7 @@
         <v>24</v>
       </c>
       <c r="BC28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
         <v>24</v>
@@ -5665,10 +5732,10 @@
         <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -5835,22 +5902,22 @@
         <v>3.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF30" t="n">
         <v>9</v>
       </c>
-      <c r="AF30" t="n">
-        <v>10</v>
-      </c>
       <c r="AG30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH30" t="n">
         <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ30" t="n">
         <v>16</v>
@@ -5889,13 +5956,13 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY30" t="n">
         <v>18</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" t="n">
         <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G31" t="n">
-        <v>0.225</v>
+        <v>0.229</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J31" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="K31" t="n">
         <v>0.448</v>
@@ -5969,7 +6036,7 @@
         <v>14.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.327</v>
+        <v>0.33</v>
       </c>
       <c r="O31" t="n">
         <v>17.8</v>
@@ -5978,22 +6045,22 @@
         <v>23.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R31" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S31" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="T31" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="U31" t="n">
         <v>20.2</v>
       </c>
       <c r="V31" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W31" t="n">
         <v>7.6</v>
@@ -6002,28 +6069,28 @@
         <v>4.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z31" t="n">
         <v>20.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>-8</v>
+        <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6038,7 +6105,7 @@
         <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6050,7 +6117,7 @@
         <v>29</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP31" t="n">
         <v>22</v>
@@ -6065,10 +6132,10 @@
         <v>30</v>
       </c>
       <c r="AT31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
@@ -6080,13 +6147,13 @@
         <v>25</v>
       </c>
       <c r="AY31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-21-2008-09</t>
+          <t>2009-03-21</t>
         </is>
       </c>
     </row>
